--- a/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>DIVINO NIÑO JESUS DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.88679</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.03648</v>
-      </c>
-      <c r="I2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.88679</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.03648</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>878 NIÑOS JESUS DEL GRAN PODER</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.88447</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.0248</v>
-      </c>
-      <c r="I3" t="n">
-        <v>221</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.88447</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.0248</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>900 ESTRELLITAS DE FATIMA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.87341</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.01827</v>
-      </c>
-      <c r="I4" t="n">
-        <v>404</v>
-      </c>
-      <c r="J4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.87341</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.01827</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>359 MANDILITO AZUL</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.89191</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.04292</v>
-      </c>
-      <c r="I5" t="n">
-        <v>275</v>
-      </c>
-      <c r="J5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.89191</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.04292</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>384 LOS AMIGUITOS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.89566</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.03117</v>
-      </c>
-      <c r="I6" t="n">
-        <v>349</v>
-      </c>
-      <c r="J6" t="n">
-        <v>18</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.89566</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.03117</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>315 LOS ANGELES Y MARIA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.89883</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.03592</v>
-      </c>
-      <c r="I7" t="n">
-        <v>442</v>
-      </c>
-      <c r="J7" t="n">
-        <v>19</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.89883</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.03592</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>3079 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.89443</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.03807</v>
-      </c>
-      <c r="I8" t="n">
-        <v>990</v>
-      </c>
-      <c r="J8" t="n">
-        <v>31</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.89443</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.03807</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>2080 ANDRES BELLO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.88691</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.02283</v>
-      </c>
-      <c r="I9" t="n">
-        <v>787</v>
-      </c>
-      <c r="J9" t="n">
-        <v>32</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.88691</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.02283</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>2051</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.872204</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.017093</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1077</v>
-      </c>
-      <c r="J10" t="n">
-        <v>39</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.872204</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.017093</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.8804</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.0048</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1047</v>
-      </c>
-      <c r="J11" t="n">
-        <v>44</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.8804</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.0048</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>8174</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.89221</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.03733</v>
-      </c>
-      <c r="I12" t="n">
-        <v>548</v>
-      </c>
-      <c r="J12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.89221</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.03733</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>8171 SAN FRANCISCO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.88255</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.02481</v>
-      </c>
-      <c r="I13" t="n">
-        <v>431</v>
-      </c>
-      <c r="J13" t="n">
-        <v>14</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.88255</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.02481</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>8168 LOS ANGELES DE NARANJAL</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.90612</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.02619</v>
-      </c>
-      <c r="I14" t="n">
-        <v>719</v>
-      </c>
-      <c r="J14" t="n">
-        <v>42</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.90612</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.02619</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>8161 MANUEL SCORZA TORRE</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.82905</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.07259000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1714</v>
-      </c>
-      <c r="J15" t="n">
-        <v>71</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.82905</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.07259</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>8155 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.89376</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.03376</v>
-      </c>
-      <c r="I16" t="n">
-        <v>602</v>
-      </c>
-      <c r="J16" t="n">
-        <v>22</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.89376</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.03376</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>3507 CAUDIVILLA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.88966</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.03147</v>
-      </c>
-      <c r="I17" t="n">
-        <v>707</v>
-      </c>
-      <c r="J17" t="n">
-        <v>27</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.88966</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.03147</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>2084</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.90217</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.03198</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1298</v>
-      </c>
-      <c r="J18" t="n">
-        <v>49</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.90217</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.03198</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>RAUL PORRAS BARRENECHEA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.89284</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.02446</v>
-      </c>
-      <c r="I19" t="n">
-        <v>938</v>
-      </c>
-      <c r="J19" t="n">
-        <v>48</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.89284</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.02446</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>3054 LA FLOR</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.89591</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.02717</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1096</v>
-      </c>
-      <c r="J20" t="n">
-        <v>53</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.89591</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.02717</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>SANTA ISABEL</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.89838</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.03579000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1228</v>
-      </c>
-      <c r="J21" t="n">
-        <v>51</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.89838</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.03579</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.87361</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.01775000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2129</v>
-      </c>
-      <c r="J22" t="n">
-        <v>97</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.87361</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.01775</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>LUCYANA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.8906</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.03264</v>
-      </c>
-      <c r="I23" t="n">
-        <v>825</v>
-      </c>
-      <c r="J23" t="n">
-        <v>46</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.8906</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.03264</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.87744</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.00593000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>712</v>
-      </c>
-      <c r="J24" t="n">
-        <v>39</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.87744</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.00593</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>597 NUESTRO SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.83058</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.06721</v>
-      </c>
-      <c r="I25" t="n">
-        <v>200</v>
-      </c>
-      <c r="J25" t="n">
-        <v>10</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.83058</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.06721</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>3074 PEDRO RUIZ GALLO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.843323</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.06224</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1373</v>
-      </c>
-      <c r="J26" t="n">
-        <v>55</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.843323</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.06224</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>5174 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.8297</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.07024</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1095</v>
-      </c>
-      <c r="J27" t="n">
-        <v>44</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.8297</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.07024</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1095</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>3519 PHILIP P. SAUNDERS</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-11.84336</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.02882</v>
-      </c>
-      <c r="I28" t="n">
-        <v>853</v>
-      </c>
-      <c r="J28" t="n">
-        <v>31</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-11.84336</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.02882</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>8175 CORAZON SAGRADO DE JESUS</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-11.85638</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.006</v>
-      </c>
-      <c r="I29" t="n">
-        <v>618</v>
-      </c>
-      <c r="J29" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-11.85638</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.006</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>8182 CORONEL JUAN VALER SANDOVAL</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-11.88505</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.03659</v>
-      </c>
-      <c r="I30" t="n">
-        <v>365</v>
-      </c>
-      <c r="J30" t="n">
-        <v>14</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-11.88505</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.03659</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>8184 SAN BENITO</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-11.81858</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.04796</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1541</v>
-      </c>
-      <c r="J31" t="n">
-        <v>58</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-11.81858</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.04796</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1541</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>JHON DALTON</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-11.89455</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.02159</v>
-      </c>
-      <c r="I32" t="n">
-        <v>313</v>
-      </c>
-      <c r="J32" t="n">
-        <v>13</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-11.89455</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.02159</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>INMACULADA CONCEPCION DE MARIA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-11.88144</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.0331</v>
-      </c>
-      <c r="I33" t="n">
-        <v>247</v>
-      </c>
-      <c r="J33" t="n">
-        <v>18</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-11.88144</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.0331</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>JESUS EL SEMBRADOR</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-11.89708</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.03673000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>221</v>
-      </c>
-      <c r="J34" t="n">
-        <v>19</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-11.89708</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.03673</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-11.87801</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.01176</v>
-      </c>
-      <c r="I35" t="n">
-        <v>581</v>
-      </c>
-      <c r="J35" t="n">
-        <v>14</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-11.87801</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.01176</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>PAMER - CARABAYLLO</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-11.89704</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.03962</v>
-      </c>
-      <c r="I36" t="n">
-        <v>209</v>
-      </c>
-      <c r="J36" t="n">
-        <v>12</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-11.89704</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.03962</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>BELEN</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-11.89561</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.03323</v>
-      </c>
-      <c r="I37" t="n">
-        <v>468</v>
-      </c>
-      <c r="J37" t="n">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-11.89561</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.03323</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-11.90065</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.03128599999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>325</v>
-      </c>
-      <c r="J38" t="n">
-        <v>22</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-11.90065</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.031286</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>CARL FRIEDRICH GAUSS</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-11.8957</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.0384</v>
-      </c>
-      <c r="I39" t="n">
-        <v>291</v>
-      </c>
-      <c r="J39" t="n">
-        <v>35</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-11.8957</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.0384</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>JEAN PIAGET</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-11.90345</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.03523</v>
-      </c>
-      <c r="I40" t="n">
-        <v>370</v>
-      </c>
-      <c r="J40" t="n">
-        <v>20</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-11.90345</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.03523</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>SAN IGNACIO DEL PROGRESO II</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-11.75119</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.96805999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>206</v>
-      </c>
-      <c r="J41" t="n">
-        <v>18</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-11.75119</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.96806</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>ANA MARIA KAN</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-11.87637</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.01775000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>236</v>
-      </c>
-      <c r="J42" t="n">
-        <v>19</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-11.87637</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.01775</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>NUESTRA SEÑORA DE COPACABANA</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-11.87434</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.01817</v>
-      </c>
-      <c r="I43" t="n">
-        <v>874</v>
-      </c>
-      <c r="J43" t="n">
-        <v>39</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-11.87434</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.01817</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-11.88478</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.03604</v>
-      </c>
-      <c r="I44" t="n">
-        <v>691</v>
-      </c>
-      <c r="J44" t="n">
-        <v>33</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-11.88478</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.03604</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>INICIATIVA</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-11.87491</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-77.01464</v>
-      </c>
-      <c r="I45" t="n">
-        <v>32</v>
-      </c>
-      <c r="J45" t="n">
-        <v>5</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-11.87491</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-77.01464</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>JESUS EDUCADOR</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-11.87363</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.02235</v>
-      </c>
-      <c r="I46" t="n">
-        <v>311</v>
-      </c>
-      <c r="J46" t="n">
-        <v>15</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-11.87363</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.02235</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-11.89174</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.02882</v>
-      </c>
-      <c r="I47" t="n">
-        <v>187</v>
-      </c>
-      <c r="J47" t="n">
-        <v>14</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-11.89174</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.02882</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>SAN JOSE DE LAS LOMAS</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-11.83005</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.08374000000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>280</v>
-      </c>
-      <c r="J48" t="n">
-        <v>18</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-11.83005</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.08374</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>STEPHEN HAWKING DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-11.880179</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-77.032794</v>
-      </c>
-      <c r="I49" t="n">
-        <v>200</v>
-      </c>
-      <c r="J49" t="n">
-        <v>9</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-11.880179</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-77.032794</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>GARCILASO DE LA VEGA DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-11.88396</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-77.03816</v>
-      </c>
-      <c r="I50" t="n">
-        <v>233</v>
-      </c>
-      <c r="J50" t="n">
-        <v>14</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-11.88396</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-77.03816</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>ELITEX</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-11.86162</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-77.00865</v>
-      </c>
-      <c r="I51" t="n">
-        <v>237</v>
-      </c>
-      <c r="J51" t="n">
-        <v>16</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-11.86162</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-77.00865</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>VIRGEN DEL CARMEN DE LUMBRERAS</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-11.83151</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-77.08233</v>
-      </c>
-      <c r="I52" t="n">
-        <v>353</v>
-      </c>
-      <c r="J52" t="n">
-        <v>23</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-11.83151</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-77.08233</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>VILLA VERITAS SCHOOL</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-11.84728</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-77.00077</v>
-      </c>
-      <c r="I53" t="n">
-        <v>310</v>
-      </c>
-      <c r="J53" t="n">
-        <v>18</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-11.84728</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-77.00077</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>REPUBLICA DE HOLANDA DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-11.89051</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-77.02585999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>48</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-11.89051</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-77.02586</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>CRISTO REDENTOR DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-11.85662</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-77.03872</v>
-      </c>
-      <c r="I55" t="n">
-        <v>727</v>
-      </c>
-      <c r="J55" t="n">
-        <v>33</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-11.85662</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-77.03872</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>GENERAL OLLANTAY</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-11.87333</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-77.01897</v>
-      </c>
-      <c r="I56" t="n">
-        <v>306</v>
-      </c>
-      <c r="J56" t="n">
-        <v>14</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-11.87333</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-77.01897</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>SAN ANTONIO DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-11.87781</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-77.02119999999999</v>
-      </c>
-      <c r="I57" t="n">
-        <v>315</v>
-      </c>
-      <c r="J57" t="n">
-        <v>16</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-11.87781</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-77.0212</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>APOLO XIII</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-11.863616</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-77.020173</v>
-      </c>
-      <c r="I58" t="n">
-        <v>300</v>
-      </c>
-      <c r="J58" t="n">
-        <v>19</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-11.863616</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-77.020173</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-11.8659</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-77.04544</v>
-      </c>
-      <c r="I59" t="n">
-        <v>378</v>
-      </c>
-      <c r="J59" t="n">
-        <v>21</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-11.8659</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-77.04544</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>MARIO BENEDETTI</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-11.842036</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-77.069602</v>
-      </c>
-      <c r="I60" t="n">
-        <v>367</v>
-      </c>
-      <c r="J60" t="n">
-        <v>22</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-11.842036</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-77.069602</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>SANTA ROSA DE VILLA</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-11.8369</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-77.07921</v>
-      </c>
-      <c r="I61" t="n">
-        <v>373</v>
-      </c>
-      <c r="J61" t="n">
-        <v>16</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-11.8369</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-77.07921</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>INNOVA SCHOOLS - CARABAYLLO ENACE</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-11.88806</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-77.03859</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1373</v>
-      </c>
-      <c r="J62" t="n">
-        <v>55</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-11.88806</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-77.03859</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>MONTECARLO DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-11.85809</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-77.01349</v>
-      </c>
-      <c r="I63" t="n">
-        <v>212</v>
-      </c>
-      <c r="J63" t="n">
-        <v>10</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-11.85809</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-77.01349</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>NUESTRA SEÑORA DE MONSERRAT DE SAN PEDRO DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-11.85542</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-77.03346999999999</v>
-      </c>
-      <c r="I64" t="n">
-        <v>386</v>
-      </c>
-      <c r="J64" t="n">
-        <v>24</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-11.85542</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-77.03347</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>8188 FE Y ESPERANZA</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-11.82473</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-77.05264</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1133</v>
-      </c>
-      <c r="J65" t="n">
-        <v>52</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-11.82473</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-77.05264</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>SKINNER</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-11.86826</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-77.02463</v>
-      </c>
-      <c r="I66" t="n">
-        <v>489</v>
-      </c>
-      <c r="J66" t="n">
-        <v>28</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-11.86826</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-77.02463</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>MI MUNDO NUEVO DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-11.89102</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-77.02489</v>
-      </c>
-      <c r="I67" t="n">
-        <v>239</v>
-      </c>
-      <c r="J67" t="n">
-        <v>13</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-11.89102</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-77.02489</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>894</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-11.88236</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-77.03488</v>
-      </c>
-      <c r="I68" t="n">
-        <v>247</v>
-      </c>
-      <c r="J68" t="n">
-        <v>8</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-11.88236</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-77.03488</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>DEMOCRACIA Y LIBERTAD</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-11.88058</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-77.00127999999999</v>
-      </c>
-      <c r="I69" t="n">
-        <v>625</v>
-      </c>
-      <c r="J69" t="n">
-        <v>38</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-11.88058</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-77.00128</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>TECHNOLOGY SCHOOLS II</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-11.872047</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-77.031741</v>
-      </c>
-      <c r="I70" t="n">
-        <v>976</v>
-      </c>
-      <c r="J70" t="n">
-        <v>49</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-11.872047</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-77.031741</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>LA CATOLICA DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-11.87814</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-77.03106</v>
-      </c>
-      <c r="I71" t="n">
-        <v>698</v>
-      </c>
-      <c r="J71" t="n">
-        <v>49</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-11.87814</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-77.03106</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>SEÑOR DE BURGOS</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-11.82114</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-77.04633</v>
-      </c>
-      <c r="I72" t="n">
-        <v>299</v>
-      </c>
-      <c r="J72" t="n">
-        <v>19</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-11.82114</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-77.04633</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>CIENTIFICO DEL NORTE</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-11.89744</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-77.04544</v>
-      </c>
-      <c r="I73" t="n">
-        <v>423</v>
-      </c>
-      <c r="J73" t="n">
-        <v>26</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-11.89744</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-77.04544</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>JACQUES COUSTEAU</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-11.85564</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-77.04488000000001</v>
-      </c>
-      <c r="I74" t="n">
-        <v>548</v>
-      </c>
-      <c r="J74" t="n">
-        <v>35</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-11.85564</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-77.04488</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>JOSE MARTI DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-11.87863</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-77.00378000000001</v>
-      </c>
-      <c r="I75" t="n">
-        <v>301</v>
-      </c>
-      <c r="J75" t="n">
-        <v>9</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-11.87863</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-77.00378</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>SANTO DOMINGO EL MAESTRO</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-11.85182</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-76.99983</v>
-      </c>
-      <c r="I76" t="n">
-        <v>625</v>
-      </c>
-      <c r="J76" t="n">
-        <v>21</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-11.85182</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-76.99983</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>JESUS DIVINO MAESTRO REDENTOR</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-11.88646</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-77.02467</v>
-      </c>
-      <c r="I77" t="n">
-        <v>396</v>
-      </c>
-      <c r="J77" t="n">
-        <v>21</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-11.88646</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-77.02467</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>THALES DE MILETO</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-11.88793</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-77.041</v>
-      </c>
-      <c r="I78" t="n">
-        <v>419</v>
-      </c>
-      <c r="J78" t="n">
-        <v>21</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-11.88793</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-77.041</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>ALMA MATER</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-11.87653</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-77.01393</v>
-      </c>
-      <c r="I79" t="n">
-        <v>201</v>
-      </c>
-      <c r="J79" t="n">
-        <v>15</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-11.87653</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-77.01393</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>SANTA ANA DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-11.883754</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-77.037617</v>
-      </c>
-      <c r="I80" t="n">
-        <v>369</v>
-      </c>
-      <c r="J80" t="n">
-        <v>19</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-11.883754</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-77.037617</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>MATEMATICO HONORES DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-11.887938</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-77.035128</v>
-      </c>
-      <c r="I81" t="n">
-        <v>253</v>
-      </c>
-      <c r="J81" t="n">
-        <v>17</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-11.887938</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-77.035128</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>CRUZ SACO DE SAN ANTONIO</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-11.86263</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-77.04522</v>
-      </c>
-      <c r="I82" t="n">
-        <v>376</v>
-      </c>
-      <c r="J82" t="n">
-        <v>19</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-11.86263</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-77.04522</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>NEUMANN SCHOOL</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-11.8671</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-77.01955</v>
-      </c>
-      <c r="I83" t="n">
-        <v>246</v>
-      </c>
-      <c r="J83" t="n">
-        <v>31</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-11.8671</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-77.01955</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>SAN AGUSTIN DE VILLA VICTORIA</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-11.84269</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-77.00414000000001</v>
-      </c>
-      <c r="I84" t="n">
-        <v>264</v>
-      </c>
-      <c r="J84" t="n">
-        <v>15</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-11.84269</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-77.00414</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>BERTOLT BRECHT</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-11.878376</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-77.032324</v>
-      </c>
-      <c r="I85" t="n">
-        <v>905</v>
-      </c>
-      <c r="J85" t="n">
-        <v>63</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-11.878376</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-77.032324</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>HISPANO AMERICANO TRINI</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-11.86387</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-77.02825</v>
-      </c>
-      <c r="I86" t="n">
-        <v>296</v>
-      </c>
-      <c r="J86" t="n">
-        <v>13</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-11.86387</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-77.02825</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>CARRUSEL</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-11.87244</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-77.01114</v>
-      </c>
-      <c r="I87" t="n">
-        <v>20</v>
-      </c>
-      <c r="J87" t="n">
-        <v>2</v>
-      </c>
-      <c r="K87" t="n">
-        <v>1</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-11.87244</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-77.01114</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>TORREBLANCA</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-11.852364</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-76.99799400000001</v>
-      </c>
-      <c r="I88" t="n">
-        <v>340</v>
-      </c>
-      <c r="J88" t="n">
-        <v>17</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-11.852364</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-76.997994</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>FAMILY SCHOOL</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-11.8441</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-77.06474</v>
-      </c>
-      <c r="I89" t="n">
-        <v>396</v>
-      </c>
-      <c r="J89" t="n">
-        <v>34</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-11.8441</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-77.06474</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>MI BUEN JESUS DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-11.87598</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-77.01824000000001</v>
-      </c>
-      <c r="I90" t="n">
-        <v>233</v>
-      </c>
-      <c r="J90" t="n">
-        <v>24</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-11.87598</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-77.01824</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>SACO OLIVEROS DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-11.85309</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-77.03673999999999</v>
-      </c>
-      <c r="I91" t="n">
-        <v>286</v>
-      </c>
-      <c r="J91" t="n">
-        <v>12</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-11.85309</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-77.03674</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>NEWTON</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-11.85364</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-77.002342</v>
-      </c>
-      <c r="I92" t="n">
-        <v>88</v>
-      </c>
-      <c r="J92" t="n">
-        <v>5</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-11.85364</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-77.002342</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>SIR NEWTON</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-11.852496</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-76.999537</v>
-      </c>
-      <c r="I93" t="n">
-        <v>390</v>
-      </c>
-      <c r="J93" t="n">
-        <v>20</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-11.852496</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-76.999537</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>MARISCAL CACERES EL TRIUNFADOR</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-11.8717</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-77.0234</v>
-      </c>
-      <c r="I94" t="n">
-        <v>287</v>
-      </c>
-      <c r="J94" t="n">
-        <v>19</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-11.8717</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-77.0234</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-11.84147</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-77.04344</v>
-      </c>
-      <c r="I95" t="n">
-        <v>242</v>
-      </c>
-      <c r="J95" t="n">
-        <v>10</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-11.84147</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-77.04344</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>NUESTRA SEÑORA DE MONSERRAT II</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-11.89406</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-77.03979</v>
-      </c>
-      <c r="I96" t="n">
-        <v>50</v>
-      </c>
-      <c r="J96" t="n">
-        <v>4</v>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-11.89406</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-77.03979</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>JESUS EDUCADOR DE LAS TORRES</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-11.855882</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-77.013052</v>
-      </c>
-      <c r="I97" t="n">
-        <v>297</v>
-      </c>
-      <c r="J97" t="n">
-        <v>14</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-11.855882</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-77.013052</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>SAN SEBASTIAN DE LIMA NORTE</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-11.89322</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-77.02605</v>
-      </c>
-      <c r="I98" t="n">
-        <v>188</v>
-      </c>
-      <c r="J98" t="n">
-        <v>16</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-11.89322</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-77.02605</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>UNIVERSITY SCHOOL</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-11.882508</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-77.033964</v>
-      </c>
-      <c r="I99" t="n">
-        <v>516</v>
-      </c>
-      <c r="J99" t="n">
-        <v>18</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-11.882508</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-77.033964</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>221596</t>
+          <t>296515</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS DE CARABAYLLO</t>
+          <t>878 NIÑOS JESUS DEL GRAN PODER</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.88679</t>
+          <t>-11.88447</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.03648</t>
+          <t>-77.0248</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>296515</t>
+          <t>296959</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>878 NIÑOS JESUS DEL GRAN PODER</t>
+          <t>597 NUESTRO SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.88447</t>
+          <t>-11.83058</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.0248</t>
+          <t>-77.06721</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>296520</t>
+          <t>655160</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>900 ESTRELLITAS DE FATIMA</t>
+          <t>MONTECARLO DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.87341</t>
+          <t>-11.85809</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.01827</t>
+          <t>-77.01349</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>296563</t>
+          <t>837603</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>359 MANDILITO AZUL</t>
+          <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.89191</t>
+          <t>-11.84147</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.04292</t>
+          <t>-77.04344</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>296596</t>
+          <t>297336</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>384 LOS AMIGUITOS</t>
+          <t>PAMER - CARABAYLLO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.89566</t>
+          <t>-11.89704</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.03117</t>
+          <t>-77.03962</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>296643</t>
+          <t>826789</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>315 LOS ANGELES Y MARIA</t>
+          <t>SACO OLIVEROS DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.89883</t>
+          <t>-11.85309</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.03592</t>
+          <t>-77.03674</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>296657</t>
+          <t>296563</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3079 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>359 MANDILITO AZUL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.89443</t>
+          <t>-11.89191</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.03807</t>
+          <t>-77.04292</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>296662</t>
+          <t>297157</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2080 ANDRES BELLO</t>
+          <t>JHON DALTON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.88691</t>
+          <t>-11.89455</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.02283</t>
+          <t>-77.02159</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>313</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>296676</t>
+          <t>708955</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>MI MUNDO NUEVO DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.872204</t>
+          <t>-11.89102</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.017093</t>
+          <t>-77.02489</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>296681</t>
+          <t>779085</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>HISPANO AMERICANO TRINI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.8804</t>
+          <t>-11.86387</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.0048</t>
+          <t>-77.02825</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>296</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>296704</t>
+          <t>296718</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8171 SAN FRANCISCO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.89221</t>
+          <t>-11.88255</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.03733</t>
+          <t>-77.02481</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>431</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,27 +1183,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>296718</t>
+          <t>297063</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8171 SAN FRANCISCO</t>
+          <t>8182 CORONEL JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.88255</t>
+          <t>-11.88505</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.02481</t>
+          <t>-77.03659</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>365</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>296737</t>
+          <t>297280</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>8168 LOS ANGELES DE NARANJAL</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.90612</t>
+          <t>-11.87801</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.02619</t>
+          <t>-77.01176</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>581</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>296761</t>
+          <t>298005</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8161 MANUEL SCORZA TORRE</t>
+          <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.82905</t>
+          <t>-11.89174</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.07259</t>
+          <t>-77.02882</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>187</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>296780</t>
+          <t>525017</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8155 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>GARCILASO DE LA VEGA DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.89376</t>
+          <t>-11.88396</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.03376</t>
+          <t>-77.03816</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>296799</t>
+          <t>602765</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3507 CAUDIVILLA</t>
+          <t>GENERAL OLLANTAY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.88966</t>
+          <t>-11.87333</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.03147</t>
+          <t>-77.01897</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>306</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>296822</t>
+          <t>847541</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>JESUS EDUCADOR DE LAS TORRES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.90217</t>
+          <t>-11.855882</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.03198</t>
+          <t>-77.013052</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>297</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>296841</t>
+          <t>297987</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RAUL PORRAS BARRENECHEA</t>
+          <t>JESUS EDUCADOR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.89284</t>
+          <t>-11.87363</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.02446</t>
+          <t>-77.02235</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>311</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>296860</t>
+          <t>712014</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3054 LA FLOR</t>
+          <t>ALMA MATER</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.89591</t>
+          <t>-11.87653</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.02717</t>
+          <t>-77.01393</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>296879</t>
+          <t>749673</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SANTA ISABEL</t>
+          <t>SAN AGUSTIN DE VILLA VICTORIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.89838</t>
+          <t>-11.84269</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.03579</t>
+          <t>-77.00414</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>296898</t>
+          <t>539156</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>ELITEX</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.87361</t>
+          <t>-11.86162</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.01775</t>
+          <t>-77.00865</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>296902</t>
+          <t>605405</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LUCYANA</t>
+          <t>SAN ANTONIO DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.8906</t>
+          <t>-11.87781</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.03264</t>
+          <t>-77.0212</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>315</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>296921</t>
+          <t>645717</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>SANTA ROSA DE VILLA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.87744</t>
+          <t>-11.8369</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.00593</t>
+          <t>-77.07921</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>373</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>296959</t>
+          <t>852603</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>597 NUESTRO SEÑOR DE LOS MILAGROS</t>
+          <t>SAN SEBASTIAN DE LIMA NORTE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.83058</t>
+          <t>-11.89322</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.06721</t>
+          <t>-77.02605</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>188</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>296978</t>
+          <t>747344</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>3074 PEDRO RUIZ GALLO</t>
+          <t>MATEMATICO HONORES DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.843323</t>
+          <t>-11.887938</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.06224</t>
+          <t>-77.035128</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>253</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>296983</t>
+          <t>802359</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5174 JUAN PABLO II</t>
+          <t>TORREBLANCA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.8297</t>
+          <t>-11.852364</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.07024</t>
+          <t>-76.997994</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>296997</t>
+          <t>296520</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3519 PHILIP P. SAUNDERS</t>
+          <t>900 ESTRELLITAS DE FATIMA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.84336</t>
+          <t>-11.87341</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.02882</t>
+          <t>-77.01827</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>404</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>297001</t>
+          <t>296596</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8175 CORAZON SAGRADO DE JESUS</t>
+          <t>384 LOS AMIGUITOS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.85638</t>
+          <t>-11.89566</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.006</t>
+          <t>-77.03117</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>349</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>297063</t>
+          <t>297176</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8182 CORONEL JUAN VALER SANDOVAL</t>
+          <t>INMACULADA CONCEPCION DE MARIA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.88505</t>
+          <t>-11.88144</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.03659</t>
+          <t>-77.0331</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>297077</t>
+          <t>297464</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8184 SAN BENITO</t>
+          <t>SAN IGNACIO DEL PROGRESO II</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.81858</t>
+          <t>-11.75119</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.04796</t>
+          <t>-76.96806</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>297157</t>
+          <t>521217</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JHON DALTON</t>
+          <t>SAN JOSE DE LAS LOMAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.89455</t>
+          <t>-11.83005</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.02159</t>
+          <t>-77.08374</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,27 +2423,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>297176</t>
+          <t>563274</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION DE MARIA</t>
+          <t>VILLA VERITAS SCHOOL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.88144</t>
+          <t>-11.84728</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.0331</t>
+          <t>-77.00077</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>297204</t>
+          <t>856168</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>JESUS EL SEMBRADOR</t>
+          <t>UNIVERSITY SCHOOL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.89708</t>
+          <t>-11.882508</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.03673</t>
+          <t>-77.033964</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>516</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>297280</t>
+          <t>296643</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>315 LOS ANGELES Y MARIA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.87801</t>
+          <t>-11.89883</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.01176</t>
+          <t>-77.03592</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>297336</t>
+          <t>297204</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PAMER - CARABAYLLO</t>
+          <t>JESUS EL SEMBRADOR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.89704</t>
+          <t>-11.89708</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.03962</t>
+          <t>-77.03673</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>297379</t>
+          <t>297572</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>ANA MARIA KAN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.89561</t>
+          <t>-11.87637</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.03323</t>
+          <t>-77.01775</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>297402</t>
+          <t>620038</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>APOLO XIII</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.90065</t>
+          <t>-11.863616</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.031286</t>
+          <t>-77.020173</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>297416</t>
+          <t>710996</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CARL FRIEDRICH GAUSS</t>
+          <t>SEÑOR DE BURGOS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.8957</t>
+          <t>-11.82114</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.0384</t>
+          <t>-77.04633</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>297435</t>
+          <t>744883</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>SANTA ANA DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.90345</t>
+          <t>-11.883754</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.03523</t>
+          <t>-77.037617</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>369</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>297464</t>
+          <t>747768</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DEL PROGRESO II</t>
+          <t>CRUZ SACO DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.75119</t>
+          <t>-11.86263</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.96806</t>
+          <t>-77.04522</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>376</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>297572</t>
+          <t>835798</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ANA MARIA KAN</t>
+          <t>MARISCAL CACERES EL TRIUNFADOR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.87637</t>
+          <t>-11.8717</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.01775</t>
+          <t>-77.0234</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>287</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>297727</t>
+          <t>780531</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE COPACABANA</t>
+          <t>CARRUSEL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.87434</t>
+          <t>-11.87244</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.01817</t>
+          <t>-77.01114</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>297751</t>
+          <t>297001</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE GUZMAN</t>
+          <t>8175 CORAZON SAGRADO DE JESUS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.88478</t>
+          <t>-11.85638</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.03604</t>
+          <t>-77.006</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>618</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>297845</t>
+          <t>297379</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>INICIATIVA</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.87491</t>
+          <t>-11.89561</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.01464</t>
+          <t>-77.03323</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>468</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>297435</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JESUS EDUCADOR</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.87363</t>
+          <t>-11.90345</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.02235</t>
+          <t>-77.03523</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>298005</t>
+          <t>834888</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SAN BENITO DE PALERMO</t>
+          <t>SIR NEWTON</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.89174</t>
+          <t>-11.852496</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.02882</t>
+          <t>-76.999537</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>390</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>521217</t>
+          <t>296704</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SAN JOSE DE LAS LOMAS</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.83005</t>
+          <t>-11.89221</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.08374</t>
+          <t>-77.03733</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>548</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>524051</t>
+          <t>626573</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>STEPHEN HAWKING DE CARABAYLLO</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.880179</t>
+          <t>-11.8659</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.032794</t>
+          <t>-77.04544</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>378</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>525017</t>
+          <t>711627</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GARCILASO DE LA VEGA DE CARABAYLLO</t>
+          <t>SANTO DOMINGO EL MAESTRO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.88396</t>
+          <t>-11.85182</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.03816</t>
+          <t>-76.99983</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>625</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>539156</t>
+          <t>711750</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ELITEX</t>
+          <t>JESUS DIVINO MAESTRO REDENTOR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.86162</t>
+          <t>-11.88646</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.00865</t>
+          <t>-77.02467</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>556457</t>
+          <t>711873</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN DE LUMBRERAS</t>
+          <t>THALES DE MILETO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.83151</t>
+          <t>-11.88793</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.08233</t>
+          <t>-77.041</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>419</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>563274</t>
+          <t>296780</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>VILLA VERITAS SCHOOL</t>
+          <t>8155 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.84728</t>
+          <t>-11.89376</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.00077</t>
+          <t>-77.03376</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>602</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>597108</t>
+          <t>297402</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>REPUBLICA DE HOLANDA DE CARABAYLLO</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.89051</t>
+          <t>-11.90065</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.02586</t>
+          <t>-77.031286</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>602746</t>
+          <t>633088</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR DE CARABAYLLO</t>
+          <t>MARIO BENEDETTI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.85662</t>
+          <t>-11.842036</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.03872</t>
+          <t>-77.069602</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>602765</t>
+          <t>556457</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GENERAL OLLANTAY</t>
+          <t>VIRGEN DEL CARMEN DE LUMBRERAS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.87333</t>
+          <t>-11.83151</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.01897</t>
+          <t>-77.08233</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>605405</t>
+          <t>699729</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE CARABAYLLO</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE SAN PEDRO DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.87781</t>
+          <t>-11.85542</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.0212</t>
+          <t>-77.03347</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>386</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>620038</t>
+          <t>813292</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>APOLO XIII</t>
+          <t>MI BUEN JESUS DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.863616</t>
+          <t>-11.87598</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.020173</t>
+          <t>-77.01824</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,17 +4035,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>626573</t>
+          <t>711076</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>CIENTIFICO DEL NORTE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.8659</t>
+          <t>-11.89744</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>423</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>633088</t>
+          <t>296799</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MARIO BENEDETTI</t>
+          <t>3507 CAUDIVILLA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.842036</t>
+          <t>-11.88966</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.069602</t>
+          <t>-77.03147</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>707</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>645717</t>
+          <t>708535</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE VILLA</t>
+          <t>SKINNER</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.8369</t>
+          <t>-11.86826</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.07921</t>
+          <t>-77.02463</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>489</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>649763</t>
+          <t>296657</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CARABAYLLO ENACE</t>
+          <t>3079 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.88806</t>
+          <t>-11.89443</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.03859</t>
+          <t>-77.03807</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>990</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>655160</t>
+          <t>296997</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MONTECARLO DE CARABAYLLO</t>
+          <t>3519 PHILIP P. SAUNDERS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.85809</t>
+          <t>-11.84336</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.01349</t>
+          <t>-77.02882</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>853</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>699729</t>
+          <t>747966</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE SAN PEDRO DE CARABAYLLO</t>
+          <t>NEUMANN SCHOOL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.85542</t>
+          <t>-11.8671</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.03347</t>
+          <t>-77.01955</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>708371</t>
+          <t>296662</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>8188 FE Y ESPERANZA</t>
+          <t>2080 ANDRES BELLO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.82473</t>
+          <t>-11.88691</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.05264</t>
+          <t>-77.02283</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>787</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>708535</t>
+          <t>297751</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SKINNER</t>
+          <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.86826</t>
+          <t>-11.88478</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.02463</t>
+          <t>-77.03604</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>691</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>708955</t>
+          <t>602746</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MI MUNDO NUEVO DE CARABAYLLO</t>
+          <t>CRISTO REDENTOR DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.89102</t>
+          <t>-11.85662</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.02489</t>
+          <t>-77.03872</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>727</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>710331</t>
+          <t>807130</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>FAMILY SCHOOL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.88236</t>
+          <t>-11.8441</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.03488</t>
+          <t>-77.06474</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>710699</t>
+          <t>297416</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DEMOCRACIA Y LIBERTAD</t>
+          <t>CARL FRIEDRICH GAUSS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-11.88058</t>
+          <t>-11.8957</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.00128</t>
+          <t>-77.0384</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>710760</t>
+          <t>711415</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS II</t>
+          <t>JACQUES COUSTEAU</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.872047</t>
+          <t>-11.85564</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.031741</t>
+          <t>-77.04488</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>548</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>710779</t>
+          <t>710699</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LA CATOLICA DE CARABAYLLO</t>
+          <t>DEMOCRACIA Y LIBERTAD</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.87814</t>
+          <t>-11.88058</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.03106</t>
+          <t>-77.00128</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>625</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>710996</t>
+          <t>296676</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SEÑOR DE BURGOS</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.82114</t>
+          <t>-11.872204</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.04633</t>
+          <t>-77.017093</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>711076</t>
+          <t>296921</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CIENTIFICO DEL NORTE</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.89744</t>
+          <t>-11.87744</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.04544</t>
+          <t>-77.00593</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>712</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>711415</t>
+          <t>297727</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JACQUES COUSTEAU</t>
+          <t>NUESTRA SEÑORA DE COPACABANA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.85564</t>
+          <t>-11.87434</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.04488</t>
+          <t>-77.01817</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>874</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,37 +5027,37 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>711533</t>
+          <t>597108</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>JOSE MARTI DE CARABAYLLO</t>
+          <t>REPUBLICA DE HOLANDA DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-11.87863</t>
+          <t>-11.89051</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.00378</t>
+          <t>-77.02586</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5089,37 +5089,37 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>711627</t>
+          <t>847348</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO EL MAESTRO</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT II</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.85182</t>
+          <t>-11.89406</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.99983</t>
+          <t>-77.03979</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>711750</t>
+          <t>296737</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>JESUS DIVINO MAESTRO REDENTOR</t>
+          <t>8168 LOS ANGELES DE NARANJAL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-11.88646</t>
+          <t>-11.90612</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.02467</t>
+          <t>-77.02619</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>719</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>711873</t>
+          <t>296681</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>THALES DE MILETO</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.88793</t>
+          <t>-11.8804</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.041</t>
+          <t>-77.0048</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>712014</t>
+          <t>296983</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ALMA MATER</t>
+          <t>5174 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-11.87653</t>
+          <t>-11.8297</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.01393</t>
+          <t>-77.07024</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>744883</t>
+          <t>296902</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SANTA ANA DE CARABAYLLO</t>
+          <t>LUCYANA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.883754</t>
+          <t>-11.8906</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.037617</t>
+          <t>-77.03264</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>825</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>747344</t>
+          <t>296841</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MATEMATICO HONORES DE CARABAYLLO</t>
+          <t>RAUL PORRAS BARRENECHEA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.887938</t>
+          <t>-11.89284</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.035128</t>
+          <t>-77.02446</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>938</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>747768</t>
+          <t>296822</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CRUZ SACO DE SAN ANTONIO</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.86263</t>
+          <t>-11.90217</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.04522</t>
+          <t>-77.03198</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>747966</t>
+          <t>710760</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NEUMANN SCHOOL</t>
+          <t>TECHNOLOGY SCHOOLS II</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.8671</t>
+          <t>-11.872047</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.01955</t>
+          <t>-77.031741</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>976</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>749673</t>
+          <t>710779</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE VILLA VICTORIA</t>
+          <t>LA CATOLICA DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.84269</t>
+          <t>-11.87814</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.00414</t>
+          <t>-77.03106</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>698</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,42 +5647,42 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>754631</t>
+          <t>297845</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BERTOLT BRECHT</t>
+          <t>INICIATIVA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-11.878376</t>
+          <t>-11.87491</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.032324</t>
+          <t>-77.01464</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5709,37 +5709,37 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>779085</t>
+          <t>828236</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HISPANO AMERICANO TRINI</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-11.86387</t>
+          <t>-11.85364</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.02825</t>
+          <t>-77.002342</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5771,37 +5771,37 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>780531</t>
+          <t>296879</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CARRUSEL</t>
+          <t>SANTA ISABEL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.87244</t>
+          <t>-11.89838</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.01114</t>
+          <t>-77.03579</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>802359</t>
+          <t>708371</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>TORREBLANCA</t>
+          <t>8188 FE Y ESPERANZA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.852364</t>
+          <t>-11.82473</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.997994</t>
+          <t>-77.05264</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>807130</t>
+          <t>296860</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FAMILY SCHOOL</t>
+          <t>3054 LA FLOR</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.8441</t>
+          <t>-11.89591</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.06474</t>
+          <t>-77.02717</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>813292</t>
+          <t>296978</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MI BUEN JESUS DE CARABAYLLO</t>
+          <t>3074 PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-11.87598</t>
+          <t>-11.843323</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.01824</t>
+          <t>-77.06224</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>826789</t>
+          <t>649763</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE CARABAYLLO</t>
+          <t>INNOVA SCHOOLS - CARABAYLLO ENACE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-11.85309</t>
+          <t>-11.88806</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.03674</t>
+          <t>-77.03859</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>828236</t>
+          <t>297077</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>8184 SAN BENITO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-11.85364</t>
+          <t>-11.81858</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.002342</t>
+          <t>-77.04796</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>834888</t>
+          <t>754631</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SIR NEWTON</t>
+          <t>BERTOLT BRECHT</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.852496</t>
+          <t>-11.878376</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-76.999537</t>
+          <t>-77.032324</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>905</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>835798</t>
+          <t>296761</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MARISCAL CACERES EL TRIUNFADOR</t>
+          <t>8161 MANUEL SCORZA TORRE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-11.8717</t>
+          <t>-11.82905</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.0234</t>
+          <t>-77.07259</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>837603</t>
+          <t>710331</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO</t>
+          <t>894</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-11.84147</t>
+          <t>-11.88236</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.04344</t>
+          <t>-77.03488</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>847348</t>
+          <t>221596</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT II</t>
+          <t>DIVINO NIÑO JESUS DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-11.89406</t>
+          <t>-11.88679</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.03979</t>
+          <t>-77.03648</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>847541</t>
+          <t>524051</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>JESUS EDUCADOR DE LAS TORRES</t>
+          <t>STEPHEN HAWKING DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-11.855882</t>
+          <t>-11.880179</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.013052</t>
+          <t>-77.032794</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>852603</t>
+          <t>711533</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN DE LIMA NORTE</t>
+          <t>JOSE MARTI DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-11.89322</t>
+          <t>-11.87863</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.02605</t>
+          <t>-77.00378</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>301</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>856168</t>
+          <t>296898</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UNIVERSITY SCHOOL</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-11.882508</t>
+          <t>-11.87361</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.033964</t>
+          <t>-77.01775</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>296515</t>
+          <t>856168</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>878 NIÑOS JESUS DEL GRAN PODER</t>
+          <t>UNIVERSITY SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.88447</t>
+          <t>516</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.0248</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-11.882508</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.033964</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>296959</t>
+          <t>852603</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>597 NUESTRO SEÑOR DE LOS MILAGROS</t>
+          <t>SAN SEBASTIAN DE LIMA NORTE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.83058</t>
+          <t>188</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.06721</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-11.89322</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.02605</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>655160</t>
+          <t>847541</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MONTECARLO DE CARABAYLLO</t>
+          <t>JESUS EDUCADOR DE LAS TORRES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.85809</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.01349</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-11.855882</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.013052</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>837603</t>
+          <t>847348</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT II</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.84147</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.04344</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-11.89406</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.03979</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>297336</t>
+          <t>837603</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PAMER - CARABAYLLO</t>
+          <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.89704</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.03962</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-11.84147</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.04344</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>826789</t>
+          <t>835798</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE CARABAYLLO</t>
+          <t>MARISCAL CACERES EL TRIUNFADOR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.85309</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.03674</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>-11.8717</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.0234</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>296563</t>
+          <t>834888</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>359 MANDILITO AZUL</t>
+          <t>SIR NEWTON</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.89191</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.04292</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-11.852496</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.999537</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>297157</t>
+          <t>828236</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JHON DALTON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.89455</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.02159</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>-11.85364</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.002342</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>708955</t>
+          <t>826789</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MI MUNDO NUEVO DE CARABAYLLO</t>
+          <t>SACO OLIVEROS DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.89102</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.02489</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-11.85309</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.03674</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>779085</t>
+          <t>813292</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HISPANO AMERICANO TRINI</t>
+          <t>MI BUEN JESUS DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.86387</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.02825</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>-11.87598</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.01824</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>296718</t>
+          <t>807130</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8171 SAN FRANCISCO</t>
+          <t>FAMILY SCHOOL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.88255</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.02481</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>-11.8441</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.06474</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>297063</t>
+          <t>802359</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8182 CORONEL JUAN VALER SANDOVAL</t>
+          <t>TORREBLANCA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.88505</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.03659</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>-11.852364</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.997994</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>297280</t>
+          <t>780531</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>CARRUSEL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.87801</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.01176</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>-11.87244</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.01114</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>298005</t>
+          <t>779085</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAN BENITO DE PALERMO</t>
+          <t>HISPANO AMERICANO TRINI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.89174</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.02882</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>-11.86387</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.02825</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>525017</t>
+          <t>754631</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GARCILASO DE LA VEGA DE CARABAYLLO</t>
+          <t>BERTOLT BRECHT</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.88396</t>
+          <t>905</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.03816</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-11.878376</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.032324</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>602765</t>
+          <t>749673</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GENERAL OLLANTAY</t>
+          <t>SAN AGUSTIN DE VILLA VICTORIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.87333</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.01897</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>-11.84269</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.00414</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>847541</t>
+          <t>747966</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JESUS EDUCADOR DE LAS TORRES</t>
+          <t>NEUMANN SCHOOL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.855882</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.013052</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>-11.8671</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.01955</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>747768</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JESUS EDUCADOR</t>
+          <t>CRUZ SACO DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.87363</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.02235</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>-11.86263</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.04522</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>712014</t>
+          <t>747344</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALMA MATER</t>
+          <t>MATEMATICO HONORES DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.87653</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.01393</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-11.887938</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.035128</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>749673</t>
+          <t>744883</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE VILLA VICTORIA</t>
+          <t>SANTA ANA DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.84269</t>
+          <t>369</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.00414</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-11.883754</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.037617</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>539156</t>
+          <t>712014</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ELITEX</t>
+          <t>ALMA MATER</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.86162</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.00865</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-11.87653</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.01393</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>605405</t>
+          <t>711873</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE CARABAYLLO</t>
+          <t>THALES DE MILETO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.87781</t>
+          <t>419</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.0212</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>-11.88793</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.041</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>645717</t>
+          <t>711750</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE VILLA</t>
+          <t>JESUS DIVINO MAESTRO REDENTOR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.8369</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.07921</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>-11.88646</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.02467</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>852603</t>
+          <t>711627</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN DE LIMA NORTE</t>
+          <t>SANTO DOMINGO EL MAESTRO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.89322</t>
+          <t>625</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.02605</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>-11.85182</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.99983</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>747344</t>
+          <t>711533</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MATEMATICO HONORES DE CARABAYLLO</t>
+          <t>JOSE MARTI DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.887938</t>
+          <t>301</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.035128</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>-11.87863</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.00378</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>802359</t>
+          <t>711415</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TORREBLANCA</t>
+          <t>JACQUES COUSTEAU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.852364</t>
+          <t>548</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.997994</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>-11.85564</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.04488</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>296520</t>
+          <t>711076</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>900 ESTRELLITAS DE FATIMA</t>
+          <t>CIENTIFICO DEL NORTE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.87341</t>
+          <t>423</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.01827</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>-11.89744</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.04544</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>296596</t>
+          <t>710996</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>384 LOS AMIGUITOS</t>
+          <t>SEÑOR DE BURGOS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.89566</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.03117</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>-11.82114</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.04633</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>297176</t>
+          <t>710779</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION DE MARIA</t>
+          <t>LA CATOLICA DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.88144</t>
+          <t>698</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.0331</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-11.87814</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.03106</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>297464</t>
+          <t>710760</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DEL PROGRESO II</t>
+          <t>TECHNOLOGY SCHOOLS II</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.75119</t>
+          <t>976</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.96806</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-11.872047</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.031741</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>521217</t>
+          <t>710699</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAN JOSE DE LAS LOMAS</t>
+          <t>DEMOCRACIA Y LIBERTAD</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.83005</t>
+          <t>625</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.08374</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-11.88058</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.00128</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>563274</t>
+          <t>710331</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VILLA VERITAS SCHOOL</t>
+          <t>894</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.84728</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.00077</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-11.88236</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.03488</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>856168</t>
+          <t>708955</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UNIVERSITY SCHOOL</t>
+          <t>MI MUNDO NUEVO DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.882508</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.033964</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>-11.89102</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.02489</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>296643</t>
+          <t>708535</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>315 LOS ANGELES Y MARIA</t>
+          <t>SKINNER</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.89883</t>
+          <t>489</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.03592</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>-11.86826</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.02463</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>297204</t>
+          <t>708371</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JESUS EL SEMBRADOR</t>
+          <t>8188 FE Y ESPERANZA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.89708</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.03673</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-11.82473</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.05264</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>297572</t>
+          <t>699729</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ANA MARIA KAN</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE SAN PEDRO DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.87637</t>
+          <t>386</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.01775</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-11.85542</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.03347</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>620038</t>
+          <t>655160</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>APOLO XIII</t>
+          <t>MONTECARLO DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.863616</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.020173</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-11.85809</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.01349</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>710996</t>
+          <t>649763</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SEÑOR DE BURGOS</t>
+          <t>INNOVA SCHOOLS - CARABAYLLO ENACE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.82114</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.04633</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-11.88806</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.03859</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>744883</t>
+          <t>645717</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SANTA ANA DE CARABAYLLO</t>
+          <t>SANTA ROSA DE VILLA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.883754</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.037617</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>-11.8369</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.07921</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>747768</t>
+          <t>633088</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CRUZ SACO DE SAN ANTONIO</t>
+          <t>MARIO BENEDETTI</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.86263</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.04522</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>-11.842036</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.069602</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>835798</t>
+          <t>626573</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MARISCAL CACERES EL TRIUNFADOR</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.8717</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.0234</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>-11.8659</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.04544</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>780531</t>
+          <t>620038</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CARRUSEL</t>
+          <t>APOLO XIII</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.87244</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.01114</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-11.863616</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-77.020173</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>297001</t>
+          <t>605405</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>8175 CORAZON SAGRADO DE JESUS</t>
+          <t>SAN ANTONIO DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.85638</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.006</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>-11.87781</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.0212</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>297379</t>
+          <t>602765</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>GENERAL OLLANTAY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.89561</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.03323</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-11.87333</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.01897</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>297435</t>
+          <t>602746</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>CRISTO REDENTOR DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.90345</t>
+          <t>727</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.03523</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>-11.85662</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.03872</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>834888</t>
+          <t>597108</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SIR NEWTON</t>
+          <t>REPUBLICA DE HOLANDA DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.852496</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.999537</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>-11.89051</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.02586</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>296704</t>
+          <t>563274</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>VILLA VERITAS SCHOOL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.89221</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.03733</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>-11.84728</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.00077</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>626573</t>
+          <t>556457</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>VIRGEN DEL CARMEN DE LUMBRERAS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.8659</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.04544</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>-11.83151</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.08233</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>711627</t>
+          <t>539156</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO EL MAESTRO</t>
+          <t>ELITEX</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.85182</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.99983</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>-11.86162</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.00865</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>711750</t>
+          <t>525017</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JESUS DIVINO MAESTRO REDENTOR</t>
+          <t>GARCILASO DE LA VEGA DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.88646</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.02467</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-11.88396</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.03816</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>711873</t>
+          <t>524051</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>THALES DE MILETO</t>
+          <t>STEPHEN HAWKING DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.88793</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.041</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>-11.880179</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.032794</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>296780</t>
+          <t>521217</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>8155 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>SAN JOSE DE LAS LOMAS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.89376</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.03376</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>-11.83005</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.08374</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>297402</t>
+          <t>298005</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.90065</t>
+          <t>187</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.031286</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-11.89174</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.02882</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>633088</t>
+          <t>297987</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MARIO BENEDETTI</t>
+          <t>JESUS EDUCADOR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.842036</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.069602</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-11.87363</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.02235</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,37 +3849,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>556457</t>
+          <t>297845</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN DE LUMBRERAS</t>
+          <t>INICIATIVA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.83151</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.08233</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-11.87491</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.01464</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>699729</t>
+          <t>297751</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE SAN PEDRO DE CARABAYLLO</t>
+          <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.85542</t>
+          <t>691</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.03347</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>-11.88478</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.03604</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>813292</t>
+          <t>297727</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MI BUEN JESUS DE CARABAYLLO</t>
+          <t>NUESTRA SEÑORA DE COPACABANA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.87598</t>
+          <t>874</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.01824</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-11.87434</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.01817</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>711076</t>
+          <t>297572</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CIENTIFICO DEL NORTE</t>
+          <t>ANA MARIA KAN</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.89744</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.04544</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>-11.87637</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.01775</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>296799</t>
+          <t>297464</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3507 CAUDIVILLA</t>
+          <t>SAN IGNACIO DEL PROGRESO II</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.88966</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.03147</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>-11.75119</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.96806</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>708535</t>
+          <t>297435</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SKINNER</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.86826</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.02463</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>-11.90345</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.03523</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>296657</t>
+          <t>297416</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>3079 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>CARL FRIEDRICH GAUSS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.89443</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.03807</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>-11.8957</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.0384</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>296997</t>
+          <t>297402</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>3519 PHILIP P. SAUNDERS</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.84336</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.02882</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>-11.90065</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.031286</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>747966</t>
+          <t>297379</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NEUMANN SCHOOL</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.8671</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.01955</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-11.89561</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.03323</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>296662</t>
+          <t>297336</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2080 ANDRES BELLO</t>
+          <t>PAMER - CARABAYLLO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.88691</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.02283</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>-11.89704</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.03962</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>297751</t>
+          <t>297280</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE GUZMAN</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.88478</t>
+          <t>581</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.03604</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>-11.87801</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.01176</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>602746</t>
+          <t>297204</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR DE CARABAYLLO</t>
+          <t>JESUS EL SEMBRADOR</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.85662</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.03872</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>-11.89708</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.03673</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>807130</t>
+          <t>297176</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FAMILY SCHOOL</t>
+          <t>INMACULADA CONCEPCION DE MARIA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.8441</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.06474</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-11.88144</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.0331</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>297416</t>
+          <t>297157</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CARL FRIEDRICH GAUSS</t>
+          <t>JHON DALTON</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-11.8957</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.0384</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-11.89455</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-77.02159</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>711415</t>
+          <t>297077</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JACQUES COUSTEAU</t>
+          <t>8184 SAN BENITO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.85564</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.04488</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>-11.81858</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-77.04796</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>710699</t>
+          <t>297063</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DEMOCRACIA Y LIBERTAD</t>
+          <t>8182 CORONEL JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.88058</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.00128</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>-11.88505</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.03659</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>296676</t>
+          <t>297001</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>8175 CORAZON SAGRADO DE JESUS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.872204</t>
+          <t>618</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.017093</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>-11.85638</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.006</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>296921</t>
+          <t>296997</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>3519 PHILIP P. SAUNDERS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.87744</t>
+          <t>853</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.00593</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>-11.84336</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.02882</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>297727</t>
+          <t>296983</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE COPACABANA</t>
+          <t>5174 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.87434</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.01817</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>-11.8297</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.07024</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,37 +5027,37 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>597108</t>
+          <t>296978</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>REPUBLICA DE HOLANDA DE CARABAYLLO</t>
+          <t>3074 PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-11.89051</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.02586</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-11.843323</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.06224</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5089,37 +5089,37 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>847348</t>
+          <t>296959</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT II</t>
+          <t>597 NUESTRO SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.89406</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.03979</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-11.83058</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.06721</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>296737</t>
+          <t>296921</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>8168 LOS ANGELES DE NARANJAL</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-11.90612</t>
+          <t>712</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.02619</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>-11.87744</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-77.00593</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>296681</t>
+          <t>296902</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>LUCYANA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.8804</t>
+          <t>825</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.0048</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>-11.8906</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.03264</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>296983</t>
+          <t>296898</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>5174 JUAN PABLO II</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-11.8297</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.07024</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>-11.87361</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.01775</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>296902</t>
+          <t>296879</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>LUCYANA</t>
+          <t>SANTA ISABEL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.8906</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.03264</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>-11.89838</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.03579</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>296841</t>
+          <t>296860</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RAUL PORRAS BARRENECHEA</t>
+          <t>3054 LA FLOR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.89284</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.02446</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>-11.89591</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.02717</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>296822</t>
+          <t>296841</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>RAUL PORRAS BARRENECHEA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.90217</t>
+          <t>938</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.03198</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>-11.89284</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-77.02446</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>710760</t>
+          <t>296822</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS II</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.872047</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.031741</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>-11.90217</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-77.03198</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>710779</t>
+          <t>296799</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>LA CATOLICA DE CARABAYLLO</t>
+          <t>3507 CAUDIVILLA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.87814</t>
+          <t>707</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.03106</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>-11.88966</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-77.03147</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,37 +5647,37 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>297845</t>
+          <t>296780</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>INICIATIVA</t>
+          <t>8155 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-11.87491</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.01464</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-11.89376</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.03376</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5709,37 +5709,37 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>828236</t>
+          <t>296761</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>8161 MANUEL SCORZA TORRE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-11.85364</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.002342</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>-11.82905</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.07259</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>296879</t>
+          <t>296737</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SANTA ISABEL</t>
+          <t>8168 LOS ANGELES DE NARANJAL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.89838</t>
+          <t>719</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.03579</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>-11.90612</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-77.02619</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>708371</t>
+          <t>296718</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>8188 FE Y ESPERANZA</t>
+          <t>8171 SAN FRANCISCO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.82473</t>
+          <t>431</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.05264</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>-11.88255</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-77.02481</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>296860</t>
+          <t>296704</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>3054 LA FLOR</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.89591</t>
+          <t>548</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.02717</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>-11.89221</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.03733</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>296978</t>
+          <t>296681</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>3074 PEDRO RUIZ GALLO</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-11.843323</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.06224</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>-11.8804</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.0048</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>649763</t>
+          <t>296676</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CARABAYLLO ENACE</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-11.88806</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.03859</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>-11.872204</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.017093</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>297077</t>
+          <t>296662</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>8184 SAN BENITO</t>
+          <t>2080 ANDRES BELLO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-11.81858</t>
+          <t>787</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.04796</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>-11.88691</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-77.02283</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>754631</t>
+          <t>296657</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BERTOLT BRECHT</t>
+          <t>3079 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.878376</t>
+          <t>990</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.032324</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>-11.89443</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-77.03807</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>296761</t>
+          <t>296643</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>8161 MANUEL SCORZA TORRE</t>
+          <t>315 LOS ANGELES Y MARIA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-11.82905</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.07259</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>-11.89883</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-77.03592</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>710331</t>
+          <t>296596</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>384 LOS AMIGUITOS</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-11.88236</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.03488</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-11.89566</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.03117</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,42 +6329,42 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>221596</t>
+          <t>296563</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS DE CARABAYLLO</t>
+          <t>359 MANDILITO AZUL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-11.88679</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.03648</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-11.89191</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.04292</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>524051</t>
+          <t>296520</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>STEPHEN HAWKING DE CARABAYLLO</t>
+          <t>900 ESTRELLITAS DE FATIMA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-11.880179</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.032794</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-11.87341</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.01827</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>711533</t>
+          <t>296515</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>JOSE MARTI DE CARABAYLLO</t>
+          <t>878 NIÑOS JESUS DEL GRAN PODER</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-11.87863</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.00378</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>-11.88447</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.0248</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,37 +6515,37 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>296898</t>
+          <t>221596</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>DIVINO NIÑO JESUS DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-11.87361</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.01775</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>-11.88679</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-77.03648</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CARABAYLLO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
